--- a/Employee_Mapping.xlsx
+++ b/Employee_Mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Avinash Agaewal\OneDrive - Lords Education &amp; Health Society\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Avinash Agaewal\OneDrive - Lords Education &amp; Health Society\Desktop\REPORT\MAPPINGS UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5702BC-C71E-4490-AEA7-EE7ADE0BA859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5385A78-F190-42D4-B711-8F83D6CF3353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0566525B-93E7-49F3-9D15-8D9A1C6AA6C8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="695">
   <si>
     <t>EMPLOYEE/VENDOR</t>
   </si>
@@ -1221,9 +1221,6 @@
     <t>Deployment</t>
   </si>
   <si>
-    <t xml:space="preserve"> Policy</t>
-  </si>
-  <si>
     <t>Tech Strategy</t>
   </si>
   <si>
@@ -2059,6 +2056,72 @@
   </si>
   <si>
     <t>Sr. Executive Finance</t>
+  </si>
+  <si>
+    <t>AI-E-287</t>
+  </si>
+  <si>
+    <t>Ram Krishna Kumar</t>
+  </si>
+  <si>
+    <t>AI-E-288</t>
+  </si>
+  <si>
+    <t>Vaidehi Martin</t>
+  </si>
+  <si>
+    <t>AI-E-289</t>
+  </si>
+  <si>
+    <t>Tushar Punjabi</t>
+  </si>
+  <si>
+    <t>AI-E-290</t>
+  </si>
+  <si>
+    <t>Aditya Bansal</t>
+  </si>
+  <si>
+    <t>AI-E-291</t>
+  </si>
+  <si>
+    <t>K. Kabi Khanganba</t>
+  </si>
+  <si>
+    <t>AI-E-292</t>
+  </si>
+  <si>
+    <t>Nikhil Lilachand Patil</t>
+  </si>
+  <si>
+    <t>AI-E-293</t>
+  </si>
+  <si>
+    <t>Techi Tapu</t>
+  </si>
+  <si>
+    <t>AI-E-294</t>
+  </si>
+  <si>
+    <t>Prathipati Shasikant</t>
+  </si>
+  <si>
+    <t>AI-E-295</t>
+  </si>
+  <si>
+    <t>Nidhi Jain</t>
+  </si>
+  <si>
+    <t>AI-E-296</t>
+  </si>
+  <si>
+    <t>Purna Bhattacharya</t>
+  </si>
+  <si>
+    <t>Instructional Designer</t>
+  </si>
+  <si>
+    <t>Senior Program Officer-Deployment</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B02CBD9C-50EC-4B85-B1CF-FDD73B7FE069}">
-  <dimension ref="A1:D268"/>
+  <dimension ref="A1:D278"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -2478,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>378</v>
@@ -2492,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>268</v>
@@ -2506,7 +2569,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>269</v>
@@ -2520,7 +2583,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>270</v>
@@ -2534,7 +2597,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>271</v>
@@ -2548,13 +2611,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>272</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -2562,7 +2625,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>273</v>
@@ -2576,7 +2639,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>274</v>
@@ -2590,7 +2653,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>275</v>
@@ -2604,7 +2667,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>276</v>
@@ -2618,13 +2681,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>277</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -2632,13 +2695,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>278</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -2646,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>279</v>
@@ -2660,7 +2723,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>280</v>
@@ -2674,7 +2737,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>281</v>
@@ -2688,7 +2751,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>270</v>
@@ -2702,7 +2765,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>282</v>
@@ -2716,7 +2779,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>283</v>
@@ -2730,7 +2793,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>284</v>
@@ -2744,7 +2807,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>273</v>
@@ -2758,7 +2821,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>285</v>
@@ -2772,7 +2835,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>286</v>
@@ -2786,7 +2849,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>287</v>
@@ -2800,13 +2863,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>288</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -2814,7 +2877,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>289</v>
@@ -2828,7 +2891,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>290</v>
@@ -2842,7 +2905,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>291</v>
@@ -2856,7 +2919,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>292</v>
@@ -2870,7 +2933,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>279</v>
@@ -2884,7 +2947,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>293</v>
@@ -2898,7 +2961,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>294</v>
@@ -2912,7 +2975,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>295</v>
@@ -2926,7 +2989,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>296</v>
@@ -2940,7 +3003,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>297</v>
@@ -2954,7 +3017,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>295</v>
@@ -2968,7 +3031,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>275</v>
@@ -2982,7 +3045,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>298</v>
@@ -2996,7 +3059,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>299</v>
@@ -3010,7 +3073,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>300</v>
@@ -3024,7 +3087,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>275</v>
@@ -3038,7 +3101,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>301</v>
@@ -3052,7 +3115,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>298</v>
@@ -3066,7 +3129,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>302</v>
@@ -3080,7 +3143,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>280</v>
@@ -3094,7 +3157,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>303</v>
@@ -3108,7 +3171,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>271</v>
@@ -3122,7 +3185,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>280</v>
@@ -3136,7 +3199,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>271</v>
@@ -3150,7 +3213,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>280</v>
@@ -3164,7 +3227,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>271</v>
@@ -3178,7 +3241,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>280</v>
@@ -3192,7 +3255,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>271</v>
@@ -3206,7 +3269,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>280</v>
@@ -3220,7 +3283,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>280</v>
@@ -3234,7 +3297,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>280</v>
@@ -3248,7 +3311,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>304</v>
@@ -3262,7 +3325,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>295</v>
@@ -3276,7 +3339,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>296</v>
@@ -3290,7 +3353,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>305</v>
@@ -3304,7 +3367,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>306</v>
@@ -3318,7 +3381,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>307</v>
@@ -3332,7 +3395,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>308</v>
@@ -3346,7 +3409,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>309</v>
@@ -3360,7 +3423,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>309</v>
@@ -3374,7 +3437,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>310</v>
@@ -3388,7 +3451,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>311</v>
@@ -3402,7 +3465,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>312</v>
@@ -3416,7 +3479,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>274</v>
@@ -3430,7 +3493,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>313</v>
@@ -3444,13 +3507,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>314</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -3458,7 +3521,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>315</v>
@@ -3472,7 +3535,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>281</v>
@@ -3486,7 +3549,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>271</v>
@@ -3500,7 +3563,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>304</v>
@@ -3514,7 +3577,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>304</v>
@@ -3528,7 +3591,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>304</v>
@@ -3542,7 +3605,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>304</v>
@@ -3556,7 +3619,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>316</v>
@@ -3570,7 +3633,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>325</v>
@@ -3584,7 +3647,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>304</v>
@@ -3598,7 +3661,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>298</v>
@@ -3612,7 +3675,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>298</v>
@@ -3626,7 +3689,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>298</v>
@@ -3640,7 +3703,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>295</v>
@@ -3654,7 +3717,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>295</v>
@@ -3668,7 +3731,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>295</v>
@@ -3682,7 +3745,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>300</v>
@@ -3696,7 +3759,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>273</v>
@@ -3710,7 +3773,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>272</v>
@@ -3724,7 +3787,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>272</v>
@@ -3738,7 +3801,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>272</v>
@@ -3752,7 +3815,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>272</v>
@@ -3766,7 +3829,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>317</v>
@@ -3780,7 +3843,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>318</v>
@@ -3794,7 +3857,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>319</v>
@@ -3808,7 +3871,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>320</v>
@@ -3822,7 +3885,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>321</v>
@@ -3836,13 +3899,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -3850,10 +3913,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>384</v>
@@ -3864,7 +3927,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>322</v>
@@ -3878,7 +3941,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>323</v>
@@ -3892,7 +3955,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>324</v>
@@ -3906,7 +3969,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>298</v>
@@ -3920,7 +3983,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>273</v>
@@ -3934,7 +3997,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>273</v>
@@ -3948,7 +4011,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>298</v>
@@ -3962,7 +4025,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>274</v>
@@ -3976,7 +4039,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>300</v>
@@ -3990,7 +4053,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>297</v>
@@ -4004,7 +4067,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>275</v>
@@ -4018,7 +4081,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>299</v>
@@ -4032,7 +4095,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>325</v>
@@ -4046,7 +4109,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>325</v>
@@ -4060,7 +4123,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>301</v>
@@ -4074,7 +4137,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>275</v>
@@ -4088,7 +4151,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>275</v>
@@ -4102,7 +4165,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>275</v>
@@ -4116,7 +4179,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>275</v>
@@ -4130,7 +4193,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>275</v>
@@ -4144,7 +4207,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>326</v>
@@ -4158,7 +4221,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>327</v>
@@ -4172,7 +4235,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>328</v>
@@ -4186,7 +4249,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>329</v>
@@ -4200,7 +4263,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>330</v>
@@ -4214,7 +4277,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>330</v>
@@ -4228,7 +4291,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>297</v>
@@ -4242,7 +4305,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>323</v>
@@ -4256,7 +4319,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>272</v>
@@ -4270,7 +4333,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>330</v>
@@ -4284,13 +4347,13 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>303</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -4298,7 +4361,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>331</v>
@@ -4312,7 +4375,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>331</v>
@@ -4326,7 +4389,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>272</v>
@@ -4340,7 +4403,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>332</v>
@@ -4354,7 +4417,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>332</v>
@@ -4368,7 +4431,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>333</v>
@@ -4382,7 +4445,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>334</v>
@@ -4396,7 +4459,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>335</v>
@@ -4410,7 +4473,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>336</v>
@@ -4424,7 +4487,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>330</v>
@@ -4438,7 +4501,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>337</v>
@@ -4452,7 +4515,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>338</v>
@@ -4466,7 +4529,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>312</v>
@@ -4480,7 +4543,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>295</v>
@@ -4494,7 +4557,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>296</v>
@@ -4508,7 +4571,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>273</v>
@@ -4522,7 +4585,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>271</v>
@@ -4536,7 +4599,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>300</v>
@@ -4550,7 +4613,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>298</v>
@@ -4564,7 +4627,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>298</v>
@@ -4578,7 +4641,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>339</v>
@@ -4592,7 +4655,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>273</v>
@@ -4606,7 +4669,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>340</v>
@@ -4620,7 +4683,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>317</v>
@@ -4634,7 +4697,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>279</v>
@@ -4648,7 +4711,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>307</v>
@@ -4662,7 +4725,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>272</v>
@@ -4676,7 +4739,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>307</v>
@@ -4690,7 +4753,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>333</v>
@@ -4704,7 +4767,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>341</v>
@@ -4718,7 +4781,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>342</v>
@@ -4732,7 +4795,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>289</v>
@@ -4746,7 +4809,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>272</v>
@@ -4760,13 +4823,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>343</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -4774,7 +4837,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>344</v>
@@ -4788,13 +4851,13 @@
         <v>165</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>345</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -4802,13 +4865,13 @@
         <v>166</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>346</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -4816,13 +4879,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>314</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -4830,7 +4893,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>272</v>
@@ -4844,13 +4907,13 @@
         <v>169</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>347</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -4858,7 +4921,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>348</v>
@@ -4872,7 +4935,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>349</v>
@@ -4886,7 +4949,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>305</v>
@@ -4900,10 +4963,10 @@
         <v>173</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>393</v>
@@ -4914,7 +4977,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>342</v>
@@ -4928,13 +4991,13 @@
         <v>175</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -4942,13 +5005,13 @@
         <v>176</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>350</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -4956,7 +5019,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>351</v>
@@ -4970,7 +5033,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>352</v>
@@ -4984,7 +5047,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>353</v>
@@ -4998,13 +5061,13 @@
         <v>180</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>351</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -5012,7 +5075,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>354</v>
@@ -5026,7 +5089,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>353</v>
@@ -5040,7 +5103,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>342</v>
@@ -5054,7 +5117,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>272</v>
@@ -5068,7 +5131,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>353</v>
@@ -5082,13 +5145,13 @@
         <v>186</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>347</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -5096,7 +5159,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>348</v>
@@ -5110,7 +5173,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>353</v>
@@ -5124,7 +5187,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>351</v>
@@ -5138,13 +5201,13 @@
         <v>190</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -5152,7 +5215,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>355</v>
@@ -5166,7 +5229,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>356</v>
@@ -5180,7 +5243,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>351</v>
@@ -5194,7 +5257,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>351</v>
@@ -5208,7 +5271,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>351</v>
@@ -5222,7 +5285,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>351</v>
@@ -5236,7 +5299,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>351</v>
@@ -5250,7 +5313,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>299</v>
@@ -5264,7 +5327,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>301</v>
@@ -5278,7 +5341,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>272</v>
@@ -5292,7 +5355,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>272</v>
@@ -5306,7 +5369,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>272</v>
@@ -5320,7 +5383,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>351</v>
@@ -5334,7 +5397,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>351</v>
@@ -5348,7 +5411,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>301</v>
@@ -5362,7 +5425,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>357</v>
@@ -5376,7 +5439,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>301</v>
@@ -5390,10 +5453,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>385</v>
@@ -5404,13 +5467,13 @@
         <v>209</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>358</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -5418,7 +5481,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>356</v>
@@ -5432,7 +5495,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>359</v>
@@ -5446,7 +5509,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>301</v>
@@ -5460,7 +5523,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>272</v>
@@ -5474,7 +5537,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>272</v>
@@ -5488,7 +5551,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>360</v>
@@ -5502,7 +5565,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>280</v>
@@ -5516,7 +5579,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>280</v>
@@ -5530,7 +5593,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>361</v>
@@ -5544,7 +5607,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>274</v>
@@ -5558,7 +5621,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C221" s="4" t="s">
         <v>362</v>
@@ -5572,7 +5635,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>295</v>
@@ -5586,7 +5649,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>272</v>
@@ -5600,7 +5663,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>363</v>
@@ -5614,7 +5677,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C225" s="4" t="s">
         <v>297</v>
@@ -5628,7 +5691,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>275</v>
@@ -5642,7 +5705,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>275</v>
@@ -5656,7 +5719,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C228" s="4" t="s">
         <v>320</v>
@@ -5670,7 +5733,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>301</v>
@@ -5684,7 +5747,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>271</v>
@@ -5698,7 +5761,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>364</v>
@@ -5712,7 +5775,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>272</v>
@@ -5726,7 +5789,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>365</v>
@@ -5740,7 +5803,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>366</v>
@@ -5754,7 +5817,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>301</v>
@@ -5768,7 +5831,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>330</v>
@@ -5782,7 +5845,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>367</v>
@@ -5796,7 +5859,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>330</v>
@@ -5810,7 +5873,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>272</v>
@@ -5824,13 +5887,13 @@
         <v>239</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>303</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -5838,7 +5901,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C241" s="4" t="s">
         <v>368</v>
@@ -5852,7 +5915,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>369</v>
@@ -5866,7 +5929,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>271</v>
@@ -5880,7 +5943,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>280</v>
@@ -5894,7 +5957,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>370</v>
@@ -5908,7 +5971,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>273</v>
@@ -5922,7 +5985,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>299</v>
@@ -5936,7 +5999,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>323</v>
@@ -5950,13 +6013,13 @@
         <v>248</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>371</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -5964,7 +6027,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>291</v>
@@ -5978,7 +6041,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>351</v>
@@ -5992,10 +6055,10 @@
         <v>251</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>383</v>
@@ -6006,7 +6069,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>372</v>
@@ -6020,7 +6083,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>294</v>
@@ -6034,7 +6097,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>271</v>
@@ -6048,7 +6111,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>280</v>
@@ -6062,7 +6125,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>373</v>
@@ -6076,7 +6139,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>271</v>
@@ -6090,7 +6153,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>374</v>
@@ -6104,7 +6167,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>351</v>
@@ -6118,7 +6181,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>351</v>
@@ -6132,7 +6195,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>271</v>
@@ -6146,7 +6209,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>330</v>
@@ -6160,7 +6223,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>375</v>
@@ -6174,7 +6237,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>295</v>
@@ -6188,13 +6251,13 @@
         <v>265</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>376</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -6202,7 +6265,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>323</v>
@@ -6216,7 +6279,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>377</v>
@@ -6225,12 +6288,148 @@
         <v>387</v>
       </c>
     </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A269" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A270" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A271" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A272" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A273" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="D273" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A274" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D274" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A275" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D275" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A276" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="D276" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A277" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D277" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A278" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D278" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D268" xr:uid="{B02CBD9C-50EC-4B85-B1CF-FDD73B7FE069}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D268">
-      <sortCondition ref="A2:A268"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:D268" xr:uid="{B02CBD9C-50EC-4B85-B1CF-FDD73B7FE069}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>